--- a/data/trans_orig/P79_n_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R-Estudios-trans_orig.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>676</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>676</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -869,22 +869,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -904,22 +904,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -945,32 +945,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8546</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -980,32 +980,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1015,22 +1015,22 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>14179</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33355</t>
+          <t>38745</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24153</t>
+          <t>28603</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44547</t>
+          <t>51817</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>48939</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33544</t>
+          <t>38959</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>59365</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>75857</t>
+          <t>87684</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61692</t>
+          <t>72580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91759</t>
+          <t>104084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -1167,67 +1167,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>69527</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45394</t>
+          <t>53730</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70125</t>
+          <t>87421</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>111956</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>97937</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>129123</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>13,62%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>97801</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>84633</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>112553</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,95%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1237,32 +1237,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>154359</t>
+          <t>181483</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134280</t>
+          <t>161269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>171736</t>
+          <t>205071</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -1278,32 +1278,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>420950</t>
+          <t>466134</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>403121</t>
+          <t>444911</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>434855</t>
+          <t>483401</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1313,32 +1313,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>607587</t>
+          <t>652566</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>590448</t>
+          <t>633712</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>624204</t>
+          <t>667902</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1348,32 +1348,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1028537</t>
+          <t>1118700</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1004966</t>
+          <t>1090688</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1052705</t>
+          <t>1144247</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -1391,17 +1391,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>705</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1687,32 +1687,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>878</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -1728,102 +1728,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29802</t>
+          <t>28976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9163</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4260</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19701</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>25372</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>15013</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>41018</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9829</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3845</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29204</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>25407</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>14262</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>48827</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1839,32 +1839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>64187</t>
+          <t>76165</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>59534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83621</t>
+          <t>98532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1874,32 +1874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>61577</t>
+          <t>73763</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42558</t>
+          <t>58481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80876</t>
+          <t>95507</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1909,32 +1909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>125764</t>
+          <t>149928</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94580</t>
+          <t>123764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152441</t>
+          <t>177035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1950,32 +1950,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>200606</t>
+          <t>232991</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>140425</t>
+          <t>199862</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>243379</t>
+          <t>272348</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1985,32 +1985,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>184941</t>
+          <t>217861</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>140359</t>
+          <t>194072</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>219301</t>
+          <t>244424</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2020,32 +2020,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>385546</t>
+          <t>450853</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>310532</t>
+          <t>409843</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>440490</t>
+          <t>495281</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -2061,32 +2061,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2008621</t>
+          <t>1903133</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1955073</t>
+          <t>1859626</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2101140</t>
+          <t>1942315</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2096,32 +2096,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1979250</t>
+          <t>1868423</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1932984</t>
+          <t>1836974</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2042174</t>
+          <t>1898376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2131,32 +2131,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3987871</t>
+          <t>3771556</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3914673</t>
+          <t>3720164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4100782</t>
+          <t>3819889</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>86,78%</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>762</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -2622,32 +2622,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>16454</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2657,32 +2657,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2692,32 +2692,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>15348</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19686</t>
+          <t>23622</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>26971</t>
+          <t>31987</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39697</t>
+          <t>45951</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2768,32 +2768,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>37824</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25100</t>
+          <t>28192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2803,32 +2803,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>60696</t>
+          <t>69811</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47642</t>
+          <t>55079</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79740</t>
+          <t>89617</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -2844,32 +2844,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>612087</t>
+          <t>670228</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>597063</t>
+          <t>654723</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>623505</t>
+          <t>682803</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2879,32 +2879,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>620146</t>
+          <t>688482</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>606743</t>
+          <t>674930</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>629828</t>
+          <t>699916</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2914,32 +2914,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1232233</t>
+          <t>1358710</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1212794</t>
+          <t>1338354</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1246574</t>
+          <t>1375027</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -2957,17 +2957,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3027,17 +3027,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3183,22 +3183,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3218,32 +3218,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10424</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3253,22 +3253,22 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>16796</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -3294,32 +3294,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9566</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>31811</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3329,32 +3329,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14317</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>26201</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3364,32 +3364,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>32678</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>54934</t>
+          <t>52146</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -3405,32 +3405,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>103920</t>
+          <t>123153</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>78747</t>
+          <t>100929</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>129013</t>
+          <t>148258</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3440,32 +3440,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>129808</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>86474</t>
+          <t>108767</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>132092</t>
+          <t>153724</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3475,32 +3475,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>213650</t>
+          <t>252961</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>179626</t>
+          <t>223371</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>246614</t>
+          <t>286915</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -3516,32 +3516,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>284135</t>
+          <t>334505</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>226246</t>
+          <t>299685</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>327792</t>
+          <t>377281</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3551,32 +3551,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>316467</t>
+          <t>367642</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>258958</t>
+          <t>334846</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>354373</t>
+          <t>402453</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3586,32 +3586,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>600602</t>
+          <t>702147</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>520050</t>
+          <t>652061</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>661701</t>
+          <t>757067</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -3627,32 +3627,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3041659</t>
+          <t>3039495</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2986391</t>
+          <t>2993778</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3123314</t>
+          <t>3082274</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3662,32 +3662,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3206983</t>
+          <t>3209471</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3159785</t>
+          <t>3169161</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3288379</t>
+          <t>3250825</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3697,32 +3697,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6248642</t>
+          <t>6248966</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6171997</t>
+          <t>6185945</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6363109</t>
+          <t>6308929</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -3740,17 +3740,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3810,17 +3810,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
